--- a/references/Mapping_DIM_LOAN_template.xlsx
+++ b/references/Mapping_DIM_LOAN_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/sb-mapping-gen/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808AEE7C-1CBB-BE46-8B17-C433855EAA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0911CAAA-FA37-264D-9AB6-BB94A71E2C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16880" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16860" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -44,12 +44,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
- (Chir lấy các tài khoản là tài khoản thuộc phân hệ MG, LD, AC - Thấu chi, AZ - Defer)</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Chir lấy các tài khoản là tài khoản thuộc phân hệ MG, LD, AC - Thấu chi, AZ - Defer)</t>
         </r>
       </text>
     </comment>
@@ -777,7 +786,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -834,19 +843,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="12"/>
@@ -890,11 +886,16 @@
     </font>
     <font>
       <b/>
-      <strike/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -983,114 +984,47 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1103,14 +1037,80 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1430,1117 +1430,1118 @@
   <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="20.5" style="19" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="37" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.33203125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="48.5" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9.1640625" style="19"/>
+    <col min="1" max="1" width="29.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="20.5" style="7" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="48.5" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="F2" s="28"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="16"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="6"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="25" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="26"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="26"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="28"/>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="17" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="15" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:6" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="33"/>
+      <c r="E10" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="17" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="35" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="36" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="21" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="29" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="34"/>
+      <c r="E16" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="17" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="34"/>
+      <c r="E17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="2" t="s">
+      <c r="D18" s="33"/>
+      <c r="E18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="5" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="5" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="1" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="5" t="s">
+      <c r="D24" s="17"/>
+      <c r="E24" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="2" t="s">
+      <c r="D25" s="17"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="33" t="s">
+      <c r="D26" s="38"/>
+      <c r="E26" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="34" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="5" t="s">
+      <c r="D27" s="17"/>
+      <c r="E27" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="5" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="5" t="s">
+      <c r="D29" s="17"/>
+      <c r="E29" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="30"/>
-      <c r="E30" s="8" t="s">
+      <c r="D30" s="16"/>
+      <c r="E30" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="17" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="D31" s="30"/>
-      <c r="E31" s="8" t="s">
+      <c r="D31" s="16"/>
+      <c r="E31" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="17" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="7" t="s">
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="8" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="7" t="s">
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="8" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="7" t="s">
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="8" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="7" t="s">
+      <c r="C35" s="8"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="8" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="7" t="s">
+      <c r="C36" s="8"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="8" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="7" t="s">
+      <c r="D37" s="31"/>
+      <c r="E37" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="7" t="s">
+      <c r="D38" s="31"/>
+      <c r="E38" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="17" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="7" t="s">
+      <c r="C39" s="8"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="17" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="7" t="s">
+      <c r="C40" s="8"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="17" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="B41" s="35" t="s">
+      <c r="B41" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D41" s="34"/>
-      <c r="E41" s="7" t="s">
+      <c r="D41" s="40"/>
+      <c r="E41" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="F41" s="2"/>
+      <c r="F41" s="17"/>
     </row>
     <row r="42" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B42" s="35" t="s">
+      <c r="B42" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="7" t="s">
+      <c r="C42" s="8"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F42" s="2"/>
+      <c r="F42" s="17"/>
     </row>
     <row r="43" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="7" t="s">
+      <c r="C43" s="8"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F43" s="2"/>
+      <c r="F43" s="17"/>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="7" t="s">
+      <c r="C44" s="8"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F44" s="2"/>
+      <c r="F44" s="17"/>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="7" t="s">
+      <c r="C45" s="8"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F45" s="2"/>
+      <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="7" t="s">
+      <c r="C46" s="8"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F46" s="2"/>
+      <c r="F46" s="17"/>
     </row>
     <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="7" t="s">
+      <c r="C47" s="8"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F47" s="2"/>
+      <c r="F47" s="17"/>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="32" t="s">
+      <c r="A48" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="7" t="s">
+      <c r="C48" s="8"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="F48" s="2"/>
+      <c r="F48" s="17"/>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="7" t="s">
+      <c r="C49" s="8"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="F49" s="2"/>
+      <c r="F49" s="17"/>
     </row>
     <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="2"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="17"/>
     </row>
     <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A51" s="32" t="s">
+      <c r="A51" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="B51" s="31" t="s">
+      <c r="B51" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="2"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="17"/>
     </row>
     <row r="52" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D52" s="30"/>
-      <c r="E52" s="7" t="s">
+      <c r="D52" s="16"/>
+      <c r="E52" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="F52" s="2"/>
+      <c r="F52" s="17"/>
     </row>
     <row r="53" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D53" s="30"/>
-      <c r="E53" s="7" t="s">
+      <c r="D53" s="16"/>
+      <c r="E53" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="F53" s="2"/>
+      <c r="F53" s="17"/>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D54" s="30"/>
-      <c r="E54" s="7" t="s">
+      <c r="D54" s="16"/>
+      <c r="E54" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="17" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D55" s="30"/>
-      <c r="E55" s="7" t="s">
+      <c r="D55" s="16"/>
+      <c r="E55" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="F55" s="2"/>
+      <c r="F55" s="17"/>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="7" t="s">
+      <c r="C56" s="8"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F56" s="2"/>
+      <c r="F56" s="17"/>
     </row>
     <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="7" t="s">
+      <c r="C57" s="8"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="F57" s="2"/>
+      <c r="F57" s="17"/>
     </row>
     <row r="58" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="7" t="s">
+      <c r="C58" s="8"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F58" s="2"/>
+      <c r="F58" s="17"/>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="7" t="s">
+      <c r="C59" s="8"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="F59" s="2"/>
+      <c r="F59" s="17"/>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="7" t="s">
+      <c r="C60" s="8"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F60" s="2"/>
+      <c r="F60" s="17"/>
     </row>
     <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D61" s="30"/>
-      <c r="E61" s="7" t="s">
+      <c r="D61" s="16"/>
+      <c r="E61" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F61" s="2"/>
+      <c r="F61" s="17"/>
     </row>
     <row r="62" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="2" t="s">
+      <c r="C62" s="8"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="17" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:6" s="38" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A63" s="20" t="s">
+    <row r="63" spans="1:6" s="15" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D63" s="39"/>
-      <c r="E63" s="20" t="s">
+      <c r="D63" s="16"/>
+      <c r="E63" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="F63" s="40"/>
+      <c r="F63" s="17"/>
     </row>
     <row r="64" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="7" t="s">
+      <c r="C64" s="8"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="F64" s="2"/>
+      <c r="F64" s="17"/>
     </row>
     <row r="65" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="7" t="s">
+      <c r="C65" s="8"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="F65" s="2"/>
+      <c r="F65" s="17"/>
     </row>
     <row r="66" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="7" t="s">
+      <c r="C66" s="8"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" s="17" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="2" t="s">
+      <c r="C67" s="8"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="17" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="2" t="s">
+      <c r="C68" s="8"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="17" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="42" t="s">
+    <row r="69" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B69" s="42"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
     </row>
     <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="37" t="s">
+      <c r="A70" s="30"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="F70" s="20" t="s">
+      <c r="F70" s="8" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B72" s="29" t="s">
+      <c r="B72" s="42" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2549,9 +2550,6 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A68:H92">
     <sortCondition ref="C68:C92"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="A69:F69"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
@@ -2579,107 +2577,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="24">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="25"/>
+      <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="24">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="24">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="12" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="24">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="24">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="12" t="s">
         <v>85</v>
       </c>
     </row>

--- a/references/Mapping_DIM_LOAN_template.xlsx
+++ b/references/Mapping_DIM_LOAN_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/sb-mapping-gen/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0911CAAA-FA37-264D-9AB6-BB94A71E2C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA249EA-A54C-2F4B-999F-0250ADEE5B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16860" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/references/Mapping_DIM_LOAN_template.xlsx
+++ b/references/Mapping_DIM_LOAN_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/sb-mapping-gen/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA249EA-A54C-2F4B-999F-0250ADEE5B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F63387-5E9B-7D4A-B6E8-946CC65D2F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16860" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Variable" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mapping!$A$5:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mapping!$A$6:$E$71</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -29,7 +29,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="229">
   <si>
     <t>Nguồn dữ liệu</t>
   </si>
@@ -143,12 +143,6 @@
   </si>
   <si>
     <t>Table description</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Bao gồm các trường màu đỏ</t>
   </si>
   <si>
     <t>DIM_LOAN</t>
@@ -780,6 +774,12 @@
 ELSE
  null
 END</t>
+  </si>
+  <si>
+    <t>Business Key</t>
+  </si>
+  <si>
+    <t>Primary Key</t>
   </si>
 </sst>
 </file>
@@ -984,7 +984,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1060,9 +1060,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1427,13 +1424,13 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.6640625" style="7" customWidth="1"/>
     <col min="2" max="2" width="20.5" style="7" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.1640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="50.33203125" style="7" customWidth="1"/>
     <col min="6" max="6" width="48.5" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9.1640625" style="7"/>
@@ -1444,13 +1441,13 @@
         <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1458,1097 +1455,1107 @@
         <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="6"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+      <c r="A4" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="21"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="6"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="D6" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="E6" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-    </row>
-    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="28"/>
+      <c r="F6" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
     </row>
     <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>86</v>
-      </c>
+      <c r="A8" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="27"/>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
-      <c r="F8" s="28"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="27"/>
+    </row>
+    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B10" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="32"/>
+      <c r="E11" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A14" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A15" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="33"/>
+      <c r="E17" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="33"/>
+      <c r="E18" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A19" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="32"/>
+      <c r="E19" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="F13" s="35" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A14" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="36" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="29" t="s">
+      <c r="C20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="34"/>
-      <c r="E16" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="34"/>
-      <c r="E17" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="31" t="s">
+      <c r="B22" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="36" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="31" t="s">
+      <c r="B23" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="31" t="s">
+      <c r="D23" s="17"/>
+      <c r="E23" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A27" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="37"/>
+      <c r="E27" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="37" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A26" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="30" t="s">
+      <c r="C29" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="D29" s="17"/>
+      <c r="E29" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A30" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A29" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="32" t="s">
-        <v>183</v>
+      <c r="C30" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="29" t="s">
+        <v>60</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>182</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>176</v>
+        <v>98</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>175</v>
       </c>
       <c r="D31" s="16"/>
-      <c r="E31" s="32" t="s">
-        <v>135</v>
+      <c r="E31" s="31" t="s">
+        <v>181</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>117</v>
+        <v>99</v>
+      </c>
+      <c r="B32" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B33" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="B34" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+        <v>108</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="31"/>
+        <v>109</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C36" s="8"/>
-      <c r="D36" s="31"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="8" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" s="31"/>
+        <v>69</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>107</v>
+        <v>123</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="30"/>
+      <c r="E38" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" s="31"/>
-      <c r="E38" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="F38" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="31"/>
+        <v>94</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="30"/>
       <c r="E39" s="8" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F41" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="B41" s="41" t="s">
-        <v>154</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D41" s="40"/>
-      <c r="E41" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F41" s="17"/>
     </row>
     <row r="42" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="B42" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="40"/>
+        <v>144</v>
+      </c>
+      <c r="B42" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" s="39"/>
       <c r="E42" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F42" s="17"/>
     </row>
     <row r="43" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B43" s="39" t="s">
-        <v>157</v>
+        <v>145</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>87</v>
       </c>
       <c r="C43" s="8"/>
-      <c r="D43" s="40"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F43" s="17"/>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>71</v>
+        <v>146</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>155</v>
       </c>
       <c r="C44" s="8"/>
-      <c r="D44" s="40"/>
+      <c r="D44" s="39"/>
       <c r="E44" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F44" s="17"/>
     </row>
     <row r="45" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>71</v>
+        <v>147</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>69</v>
       </c>
       <c r="C45" s="8"/>
-      <c r="D45" s="40"/>
+      <c r="D45" s="39"/>
       <c r="E45" s="8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="B46" s="39" t="s">
-        <v>156</v>
+        <v>148</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>69</v>
       </c>
       <c r="C46" s="8"/>
-      <c r="D46" s="40"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F46" s="17"/>
     </row>
     <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B47" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="38" t="s">
         <v>154</v>
       </c>
       <c r="C47" s="8"/>
-      <c r="D47" s="40"/>
+      <c r="D47" s="39"/>
       <c r="E47" s="8" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F47" s="17"/>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="B48" s="39" t="s">
-        <v>155</v>
+        <v>150</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>152</v>
       </c>
       <c r="C48" s="8"/>
-      <c r="D48" s="40"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F48" s="17"/>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="B49" s="39" t="s">
-        <v>154</v>
+        <v>151</v>
+      </c>
+      <c r="B49" s="38" t="s">
+        <v>153</v>
       </c>
       <c r="C49" s="8"/>
-      <c r="D49" s="40"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="8" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F49" s="17"/>
     </row>
     <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="B50" s="39" t="s">
-        <v>94</v>
+        <v>166</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>152</v>
       </c>
       <c r="C50" s="8"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="8"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="F50" s="17"/>
     </row>
     <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="B51" s="39" t="s">
-        <v>172</v>
+        <v>168</v>
+      </c>
+      <c r="B51" s="38" t="s">
+        <v>92</v>
       </c>
       <c r="C51" s="8"/>
-      <c r="D51" s="40"/>
+      <c r="D51" s="39"/>
       <c r="E51" s="8"/>
       <c r="F51" s="17"/>
     </row>
-    <row r="52" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B52" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="8" t="s">
-        <v>227</v>
-      </c>
+    <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A52" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52" s="8"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="8"/>
       <c r="F52" s="17"/>
     </row>
     <row r="53" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>90</v>
+        <v>172</v>
+      </c>
+      <c r="B53" s="38" t="s">
+        <v>97</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D53" s="16"/>
       <c r="E53" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F53" s="17"/>
     </row>
-    <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D54" s="16"/>
       <c r="E54" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>182</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="F54" s="17"/>
     </row>
     <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D55" s="16"/>
       <c r="E55" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="F55" s="17"/>
+        <v>179</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C56" s="8"/>
+      <c r="C56" s="8" t="s">
+        <v>186</v>
+      </c>
       <c r="D56" s="16"/>
       <c r="E56" s="8" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F56" s="17"/>
     </row>
     <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="16"/>
       <c r="E57" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F57" s="17"/>
     </row>
     <row r="58" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="16"/>
       <c r="E58" s="8" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F58" s="17"/>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="16"/>
       <c r="E59" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F59" s="17"/>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="16"/>
       <c r="E60" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F60" s="17"/>
     </row>
     <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>195</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C61" s="8"/>
       <c r="D61" s="16"/>
       <c r="E61" s="8" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F61" s="17"/>
     </row>
     <row r="62" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D62" s="16"/>
+      <c r="E62" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F62" s="17"/>
+    </row>
+    <row r="63" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C63" s="8"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="B62" s="8" t="s">
+    </row>
+    <row r="64" spans="1:6" s="15" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A64" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="17" t="s">
+      <c r="B64" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" s="15" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A63" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="D63" s="16"/>
-      <c r="E63" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="F63" s="17"/>
-    </row>
-    <row r="64" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C64" s="8"/>
       <c r="D64" s="16"/>
       <c r="E64" s="8" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F64" s="17"/>
     </row>
     <row r="65" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="16"/>
       <c r="E65" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F65" s="17"/>
     </row>
     <row r="66" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>217</v>
+        <v>89</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="16"/>
       <c r="E66" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F66" s="17" t="s">
-        <v>219</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="F66" s="17"/>
     </row>
     <row r="67" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>89</v>
+        <v>215</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="16"/>
-      <c r="E67" s="8"/>
+      <c r="E67" s="8" t="s">
+        <v>216</v>
+      </c>
       <c r="F67" s="17" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="16"/>
       <c r="E68" s="8"/>
       <c r="F68" s="17" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="18"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18"/>
-    </row>
-    <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" s="30"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B72" s="42" t="s">
-        <v>126</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A69" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="8"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+    </row>
+    <row r="71" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A71" s="29"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B73" s="41" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:E70" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A68:H92">
-    <sortCondition ref="C68:C92"/>
+  <autoFilter ref="A6:E71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A69:H93">
+    <sortCondition ref="C69:C93"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2578,24 +2585,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="D2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -2603,13 +2610,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>70</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="E3" s="12"/>
     </row>
@@ -2618,16 +2625,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -2635,16 +2642,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -2652,16 +2659,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -2669,16 +2676,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>83</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
